--- a/danish_grid_cleaned.xlsx
+++ b/danish_grid_cleaned.xlsx
@@ -1666,10 +1666,10 @@
         <v>132</v>
       </c>
       <c r="F43" t="n">
-        <v>11.807</v>
+        <v>11.8779697766085</v>
       </c>
       <c r="G43" t="n">
-        <v>55.279</v>
+        <v>55.2357925836045</v>
       </c>
     </row>
     <row r="44">
@@ -2192,8 +2192,12 @@
       <c r="E62" t="n">
         <v>132</v>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>11.3484666229282</v>
+      </c>
+      <c r="G62" t="n">
+        <v>54.6672570217212</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5254,8 +5258,12 @@
       <c r="E172" t="n">
         <v>132</v>
       </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="F172" t="n">
+        <v>12.5493736552885</v>
+      </c>
+      <c r="G172" t="n">
+        <v>56.0227956884244</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5678,8 +5686,12 @@
       <c r="E188" t="n">
         <v>132</v>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>11.6516548385523</v>
+      </c>
+      <c r="G188" t="n">
+        <v>55.5471211604433</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -5704,10 +5716,10 @@
         <v>132</v>
       </c>
       <c r="F189" t="n">
-        <v>11.956</v>
+        <v>11.8557070098871</v>
       </c>
       <c r="G189" t="n">
-        <v>54.943</v>
+        <v>54.9591951885506</v>
       </c>
     </row>
     <row r="190">
@@ -5816,10 +5828,10 @@
         <v>9</v>
       </c>
       <c r="F193" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="G193" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
     </row>
     <row r="194">
@@ -5845,10 +5857,10 @@
         <v>132</v>
       </c>
       <c r="F194" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="G194" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
     </row>
     <row r="195">
@@ -5931,8 +5943,12 @@
       <c r="E197" t="n">
         <v>132</v>
       </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
+      <c r="F197" t="n">
+        <v>11.6329045846498</v>
+      </c>
+      <c r="G197" t="n">
+        <v>54.620413968645</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -5956,8 +5972,12 @@
       <c r="E198" t="n">
         <v>132</v>
       </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
+      <c r="F198" t="n">
+        <v>11.6789685278067</v>
+      </c>
+      <c r="G198" t="n">
+        <v>54.5830580005068</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -6479,8 +6499,12 @@
       <c r="E217" t="n">
         <v>132</v>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="F217" t="n">
+        <v>12.4328805295857</v>
+      </c>
+      <c r="G217" t="n">
+        <v>55.9265355389099</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -6753,8 +6777,12 @@
       <c r="E227" t="n">
         <v>400</v>
       </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
+      <c r="F227" t="n">
+        <v>12.7085299819776</v>
+      </c>
+      <c r="G227" t="n">
+        <v>56.0493550090635</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -6774,8 +6802,12 @@
       <c r="E228" t="n">
         <v>400</v>
       </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
+      <c r="F228" t="n">
+        <v>12.7085299819776</v>
+      </c>
+      <c r="G228" t="n">
+        <v>56.0493550090635</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7600,8 +7632,12 @@
       <c r="E258" t="n">
         <v>132</v>
       </c>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="F258" t="n">
+        <v>11.218752272215</v>
+      </c>
+      <c r="G258" t="n">
+        <v>54.8451095369072</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8965,8 +9001,12 @@
         <v>3</v>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>56.0493550090635</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12.7085299819776</v>
+      </c>
       <c r="R4" t="n">
         <v>400</v>
       </c>
@@ -9042,8 +9082,12 @@
         <v>2</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>56.0493550090635</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12.7085299819776</v>
+      </c>
       <c r="R5" t="n">
         <v>400</v>
       </c>
@@ -11465,8 +11509,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="V35" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="W35" t="n">
         <v>132</v>
       </c>
@@ -11546,8 +11594,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="V36" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="W36" t="n">
         <v>132</v>
       </c>
@@ -11716,8 +11768,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="V38" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="W38" t="n">
         <v>132</v>
       </c>
@@ -11805,8 +11861,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="U39" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="V39" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="W39" t="n">
         <v>132</v>
       </c>
@@ -11984,10 +12044,10 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="V41" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="W41" t="n">
         <v>132</v>
@@ -12170,10 +12230,10 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="V43" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="W43" t="n">
         <v>132</v>
@@ -12787,8 +12847,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="R50" t="n">
         <v>132</v>
       </c>
@@ -12800,8 +12864,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="V50" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="W50" t="n">
         <v>132</v>
       </c>
@@ -12872,8 +12940,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="R51" t="n">
         <v>132</v>
       </c>
@@ -12961,8 +13033,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="R52" t="n">
         <v>132</v>
       </c>
@@ -13050,8 +13126,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="R53" t="n">
         <v>132</v>
       </c>
@@ -13414,8 +13494,12 @@
           <t>Vestlolland</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>54.8451095369072</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>11.218752272215</v>
+      </c>
       <c r="R57" t="n">
         <v>132</v>
       </c>
@@ -13503,8 +13587,12 @@
           <t>Vestlolland</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>54.8451095369072</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>11.218752272215</v>
+      </c>
       <c r="R58" t="n">
         <v>132</v>
       </c>
@@ -13517,10 +13605,10 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="V58" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="W58" t="n">
         <v>132</v>
@@ -13888,8 +13976,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="V62" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="W62" t="n">
         <v>132</v>
       </c>
@@ -17326,10 +17418,10 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>55.279</v>
+        <v>55.2357925836045</v>
       </c>
       <c r="Q100" t="n">
-        <v>11.807</v>
+        <v>11.8779697766085</v>
       </c>
       <c r="R100" t="n">
         <v>132</v>
@@ -17419,10 +17511,10 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>55.279</v>
+        <v>55.2357925836045</v>
       </c>
       <c r="Q101" t="n">
-        <v>11.807</v>
+        <v>11.8779697766085</v>
       </c>
       <c r="R101" t="n">
         <v>132</v>
@@ -17512,10 +17604,10 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>55.279</v>
+        <v>55.2357925836045</v>
       </c>
       <c r="Q102" t="n">
-        <v>11.807</v>
+        <v>11.8779697766085</v>
       </c>
       <c r="R102" t="n">
         <v>132</v>
@@ -17529,10 +17621,10 @@
         </is>
       </c>
       <c r="U102" t="n">
-        <v>54.943</v>
+        <v>54.9591951885506</v>
       </c>
       <c r="V102" t="n">
-        <v>11.956</v>
+        <v>11.8557070098871</v>
       </c>
       <c r="W102" t="n">
         <v>132</v>
@@ -17605,10 +17697,10 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>55.279</v>
+        <v>55.2357925836045</v>
       </c>
       <c r="Q103" t="n">
-        <v>11.807</v>
+        <v>11.8779697766085</v>
       </c>
       <c r="R103" t="n">
         <v>132</v>
@@ -19240,10 +19332,10 @@
         </is>
       </c>
       <c r="U121" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="V121" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="W121" t="n">
         <v>132</v>
@@ -19315,8 +19407,12 @@
           <t>132 KV STATION FEMERN</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
+      <c r="P122" t="n">
+        <v>54.6672570217212</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>11.3484666229282</v>
+      </c>
       <c r="R122" t="n">
         <v>132</v>
       </c>
@@ -19404,8 +19500,12 @@
           <t>132 KV STATION FEMERN</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
+      <c r="P123" t="n">
+        <v>54.6672570217212</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>11.3484666229282</v>
+      </c>
       <c r="R123" t="n">
         <v>132</v>
       </c>
@@ -19417,8 +19517,12 @@
           <t>Vestlolland</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
+      <c r="U123" t="n">
+        <v>54.8451095369072</v>
+      </c>
+      <c r="V123" t="n">
+        <v>11.218752272215</v>
+      </c>
       <c r="W123" t="n">
         <v>132</v>
       </c>
@@ -20210,8 +20314,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr"/>
-      <c r="V132" t="inlineStr"/>
+      <c r="U132" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="V132" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="W132" t="n">
         <v>132</v>
       </c>
@@ -20384,8 +20492,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
+      <c r="U134" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="V134" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="W134" t="n">
         <v>132</v>
       </c>
@@ -21193,8 +21305,12 @@
           <t>Nyrup</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
+      <c r="U143" t="n">
+        <v>55.5471211604433</v>
+      </c>
+      <c r="V143" t="n">
+        <v>11.6516548385523</v>
+      </c>
       <c r="W143" t="n">
         <v>132</v>
       </c>
@@ -25148,8 +25264,12 @@
           <t>Nyrup</t>
         </is>
       </c>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
+      <c r="P187" t="n">
+        <v>55.5471211604433</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>11.6516548385523</v>
+      </c>
       <c r="R187" t="n">
         <v>132</v>
       </c>
@@ -25233,8 +25353,12 @@
           <t>Nyrup</t>
         </is>
       </c>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
+      <c r="P188" t="n">
+        <v>55.5471211604433</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>11.6516548385523</v>
+      </c>
       <c r="R188" t="n">
         <v>132</v>
       </c>
@@ -25323,10 +25447,10 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>54.943</v>
+        <v>54.9591951885506</v>
       </c>
       <c r="Q189" t="n">
-        <v>11.956</v>
+        <v>11.8557070098871</v>
       </c>
       <c r="R189" t="n">
         <v>132</v>
@@ -25340,10 +25464,10 @@
         </is>
       </c>
       <c r="U189" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="V189" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="W189" t="n">
         <v>132</v>
@@ -25416,10 +25540,10 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>54.943</v>
+        <v>54.9591951885506</v>
       </c>
       <c r="Q190" t="n">
-        <v>11.956</v>
+        <v>11.8557070098871</v>
       </c>
       <c r="R190" t="n">
         <v>132</v>
@@ -25433,10 +25557,10 @@
         </is>
       </c>
       <c r="U190" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="V190" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="W190" t="n">
         <v>132</v>
@@ -25509,10 +25633,10 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>54.943</v>
+        <v>54.9591951885506</v>
       </c>
       <c r="Q191" t="n">
-        <v>11.956</v>
+        <v>11.8557070098871</v>
       </c>
       <c r="R191" t="n">
         <v>132</v>
@@ -25602,10 +25726,10 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="Q192" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="R192" t="n">
         <v>132</v>
@@ -25695,10 +25819,10 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="Q193" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="R193" t="n">
         <v>132</v>
@@ -25711,8 +25835,12 @@
           <t>VINDMØLLEPARK RØDSAND 2</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
+      <c r="U193" t="n">
+        <v>54.620413968645</v>
+      </c>
+      <c r="V193" t="n">
+        <v>11.6329045846498</v>
+      </c>
       <c r="W193" t="n">
         <v>132</v>
       </c>
@@ -25784,10 +25912,10 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>54.753</v>
+        <v>54.7964103459532</v>
       </c>
       <c r="Q194" t="n">
-        <v>11.895</v>
+        <v>11.6963335557349</v>
       </c>
       <c r="R194" t="n">
         <v>132</v>
@@ -25800,8 +25928,12 @@
           <t>132 KV VINDMØLLEPARK RØDSAND 1</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
+      <c r="U194" t="n">
+        <v>54.5830580005068</v>
+      </c>
+      <c r="V194" t="n">
+        <v>11.6789685278067</v>
+      </c>
       <c r="W194" t="n">
         <v>132</v>
       </c>
@@ -26232,8 +26364,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
+      <c r="P199" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="R199" t="n">
         <v>132</v>
       </c>
@@ -26245,8 +26381,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr"/>
+      <c r="U199" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="V199" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="W199" t="n">
         <v>132</v>
       </c>
@@ -26317,8 +26457,12 @@
           <t>Stasevang</t>
         </is>
       </c>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
+      <c r="P200" t="n">
+        <v>55.9265355389099</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>12.4328805295857</v>
+      </c>
       <c r="R200" t="n">
         <v>132</v>
       </c>
@@ -26330,8 +26474,12 @@
           <t>Teglstrupgård</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr"/>
+      <c r="U200" t="n">
+        <v>56.0227956884244</v>
+      </c>
+      <c r="V200" t="n">
+        <v>12.5493736552885</v>
+      </c>
       <c r="W200" t="n">
         <v>132</v>
       </c>
@@ -26419,8 +26567,12 @@
           <t>Vestlolland</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
+      <c r="U201" t="n">
+        <v>54.8451095369072</v>
+      </c>
+      <c r="V201" t="n">
+        <v>11.218752272215</v>
+      </c>
       <c r="W201" t="n">
         <v>132</v>
       </c>

--- a/danish_grid_cleaned.xlsx
+++ b/danish_grid_cleaned.xlsx
@@ -546,8 +546,12 @@
       <c r="E4" t="n">
         <v>165</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>9.907020240291439</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57.0217673874711</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1852,8 +1856,12 @@
       <c r="E50" t="n">
         <v>132</v>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>12.3850960105833</v>
+      </c>
+      <c r="G50" t="n">
+        <v>55.7471878040055</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1906,8 +1914,12 @@
       <c r="E52" t="n">
         <v>132</v>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>12.4051289650067</v>
+      </c>
+      <c r="G52" t="n">
+        <v>55.7020042516207</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2395,8 +2407,12 @@
       <c r="E69" t="n">
         <v>132</v>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>12.2977578306887</v>
+      </c>
+      <c r="G69" t="n">
+        <v>55.5990778622218</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2673,8 +2689,12 @@
       <c r="E79" t="n">
         <v>10</v>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>12.5371757349425</v>
+      </c>
+      <c r="G79" t="n">
+        <v>55.7611873025953</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2698,8 +2718,12 @@
       <c r="E80" t="n">
         <v>10</v>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>12.5371757349425</v>
+      </c>
+      <c r="G80" t="n">
+        <v>55.7611873025953</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2723,8 +2747,12 @@
       <c r="E81" t="n">
         <v>132</v>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>12.5371757349425</v>
+      </c>
+      <c r="G81" t="n">
+        <v>55.7611873025953</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2748,8 +2776,12 @@
       <c r="E82" t="n">
         <v>400</v>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>12.5371757349425</v>
+      </c>
+      <c r="G82" t="n">
+        <v>55.7611873025953</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2773,8 +2805,12 @@
       <c r="E83" t="n">
         <v>132</v>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>12.4642636962795</v>
+      </c>
+      <c r="G83" t="n">
+        <v>55.7432900024616</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2914,8 +2950,12 @@
       <c r="E88" t="n">
         <v>165</v>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>10.16805</v>
+      </c>
+      <c r="G88" t="n">
+        <v>56.1904355183995</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3055,8 +3095,12 @@
       <c r="E93" t="n">
         <v>132</v>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>12.1048418993376</v>
+      </c>
+      <c r="G93" t="n">
+        <v>55.6530094301176</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3138,8 +3182,12 @@
       <c r="E96" t="n">
         <v>10</v>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>11.3420209912948</v>
+      </c>
+      <c r="G96" t="n">
+        <v>55.5217287348645</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3163,8 +3211,12 @@
       <c r="E97" t="n">
         <v>15.8</v>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>11.3420209912948</v>
+      </c>
+      <c r="G97" t="n">
+        <v>55.5217287348645</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3188,8 +3240,12 @@
       <c r="E98" t="n">
         <v>400</v>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>11.3420209912948</v>
+      </c>
+      <c r="G98" t="n">
+        <v>55.5217287348645</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3242,8 +3298,12 @@
       <c r="E100" t="n">
         <v>165</v>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>9.95490572883609</v>
+      </c>
+      <c r="G100" t="n">
+        <v>56.482077640062</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3383,8 +3443,12 @@
       <c r="E105" t="n">
         <v>165</v>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>10.1426557207713</v>
+      </c>
+      <c r="G105" t="n">
+        <v>56.1493883098031</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3408,8 +3472,12 @@
       <c r="E106" t="n">
         <v>132</v>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>12.3880574948221</v>
+      </c>
+      <c r="G106" t="n">
+        <v>55.759540142335</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3433,8 +3501,12 @@
       <c r="E107" t="n">
         <v>132</v>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>12.3561289035921</v>
+      </c>
+      <c r="G107" t="n">
+        <v>55.6599589670042</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3458,8 +3530,12 @@
       <c r="E108" t="n">
         <v>132</v>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>12.2272856189554</v>
+      </c>
+      <c r="G108" t="n">
+        <v>55.7893040846295</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3483,8 +3559,12 @@
       <c r="E109" t="n">
         <v>400</v>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>12.2272856189554</v>
+      </c>
+      <c r="G109" t="n">
+        <v>55.7893040846295</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3537,8 +3617,12 @@
       <c r="E111" t="n">
         <v>165</v>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>9.91458276509298</v>
+      </c>
+      <c r="G111" t="n">
+        <v>57.0463253989495</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3931,8 +4015,12 @@
       <c r="E125" t="n">
         <v>132</v>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>12.6541582684112</v>
+      </c>
+      <c r="G125" t="n">
+        <v>55.6345721923086</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3985,8 +4073,12 @@
       <c r="E127" t="n">
         <v>132</v>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>12.1207776388374</v>
+      </c>
+      <c r="G127" t="n">
+        <v>55.6476215230415</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4503,8 +4595,12 @@
       <c r="E145" t="n">
         <v>132</v>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="F145" t="n">
+        <v>11.8863748101793</v>
+      </c>
+      <c r="G145" t="n">
+        <v>55.6248540827926</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4785,8 +4881,12 @@
       <c r="E155" t="n">
         <v>165</v>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+      <c r="F155" t="n">
+        <v>8.353226184389969</v>
+      </c>
+      <c r="G155" t="n">
+        <v>56.1093866151184</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5013,8 +5113,12 @@
       <c r="E163" t="n">
         <v>165</v>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
+      <c r="F163" t="n">
+        <v>10.4987386757303</v>
+      </c>
+      <c r="G163" t="n">
+        <v>56.435023192998</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5154,8 +5258,12 @@
       <c r="E168" t="n">
         <v>165</v>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+      <c r="F168" t="n">
+        <v>10.2190107413707</v>
+      </c>
+      <c r="G168" t="n">
+        <v>56.225273912857</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5179,8 +5287,12 @@
       <c r="E169" t="n">
         <v>165</v>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+      <c r="F169" t="n">
+        <v>10.0985712474414</v>
+      </c>
+      <c r="G169" t="n">
+        <v>56.4297672454752</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5233,8 +5345,12 @@
       <c r="E171" t="n">
         <v>132</v>
       </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
+      <c r="F171" t="n">
+        <v>12.2742303637046</v>
+      </c>
+      <c r="G171" t="n">
+        <v>55.5685451629065</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5495,8 +5611,12 @@
       <c r="E181" t="n">
         <v>132</v>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="F181" t="n">
+        <v>11.1176852759734</v>
+      </c>
+      <c r="G181" t="n">
+        <v>55.6873745837978</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -5744,8 +5864,12 @@
       <c r="E190" t="n">
         <v>132</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>11.9453047753712</v>
+      </c>
+      <c r="G190" t="n">
+        <v>55.6705744166352</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6146,8 +6270,12 @@
       <c r="E204" t="n">
         <v>165</v>
       </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="F204" t="n">
+        <v>9.73224881349171</v>
+      </c>
+      <c r="G204" t="n">
+        <v>55.5984310487063</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -6345,8 +6473,12 @@
       <c r="E211" t="n">
         <v>165</v>
       </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
+      <c r="F211" t="n">
+        <v>9.931709330517711</v>
+      </c>
+      <c r="G211" t="n">
+        <v>57.0715877870094</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -6399,8 +6531,12 @@
       <c r="E213" t="n">
         <v>132</v>
       </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
+      <c r="F213" t="n">
+        <v>12.5878763748329</v>
+      </c>
+      <c r="G213" t="n">
+        <v>55.7144797446461</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -7301,10 +7437,10 @@
         <v>132</v>
       </c>
       <c r="F246" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="G246" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
     </row>
     <row r="247">
@@ -11258,8 +11394,12 @@
           <t>400 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="V32" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="W32" t="n">
         <v>400</v>
       </c>
@@ -11670,8 +11810,12 @@
           <t>400 KV KOBLINGSSTATION HERSLEV</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>55.5217287348645</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>11.3420209912948</v>
+      </c>
       <c r="R37" t="n">
         <v>400</v>
       </c>
@@ -11937,8 +12081,12 @@
           <t>Ejbygård</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>55.7020042516207</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>12.4051289650067</v>
+      </c>
       <c r="R40" t="n">
         <v>132</v>
       </c>
@@ -12504,8 +12652,12 @@
           <t>Novo Syd</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>55.6873745837978</v>
+      </c>
+      <c r="V46" t="n">
+        <v>11.1176852759734</v>
+      </c>
       <c r="W46" t="n">
         <v>132</v>
       </c>
@@ -12593,8 +12745,12 @@
           <t>Novo Syd</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>55.6873745837978</v>
+      </c>
+      <c r="V47" t="n">
+        <v>11.1176852759734</v>
+      </c>
       <c r="W47" t="n">
         <v>132</v>
       </c>
@@ -13402,10 +13558,10 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
       <c r="Q56" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="R56" t="n">
         <v>132</v>
@@ -14534,8 +14690,12 @@
           <t>Kastrup Koblingstation</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="U68" t="n">
+        <v>55.6345721923086</v>
+      </c>
+      <c r="V68" t="n">
+        <v>12.6541582684112</v>
+      </c>
       <c r="W68" t="n">
         <v>132</v>
       </c>
@@ -14716,8 +14876,12 @@
           <t>Glentegård</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+      <c r="U70" t="n">
+        <v>55.7611873025953</v>
+      </c>
+      <c r="V70" t="n">
+        <v>12.5371757349425</v>
+      </c>
       <c r="W70" t="n">
         <v>132</v>
       </c>
@@ -14898,8 +15062,12 @@
           <t>Kastrup Koblingstation</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="U72" t="n">
+        <v>55.6345721923086</v>
+      </c>
+      <c r="V72" t="n">
+        <v>12.6541582684112</v>
+      </c>
       <c r="W72" t="n">
         <v>132</v>
       </c>
@@ -14987,8 +15155,12 @@
           <t>132 KV SVANEMØLLE KBST</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
+      <c r="U73" t="n">
+        <v>55.7144797446461</v>
+      </c>
+      <c r="V73" t="n">
+        <v>12.5878763748329</v>
+      </c>
       <c r="W73" t="n">
         <v>132</v>
       </c>
@@ -15076,8 +15248,12 @@
           <t>132 KV SVANEMØLLE KBST</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+      <c r="U74" t="n">
+        <v>55.7144797446461</v>
+      </c>
+      <c r="V74" t="n">
+        <v>12.5878763748329</v>
+      </c>
       <c r="W74" t="n">
         <v>132</v>
       </c>
@@ -15618,8 +15794,12 @@
           <t>400 KV KOBLINGSSTATION HERSLEV</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
+      <c r="U80" t="n">
+        <v>55.5217287348645</v>
+      </c>
+      <c r="V80" t="n">
+        <v>11.3420209912948</v>
+      </c>
       <c r="W80" t="n">
         <v>400</v>
       </c>
@@ -16265,8 +16445,12 @@
           <t>Grønnegård</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
+      <c r="U87" t="n">
+        <v>55.7432900024616</v>
+      </c>
+      <c r="V87" t="n">
+        <v>12.4642636962795</v>
+      </c>
       <c r="W87" t="n">
         <v>132</v>
       </c>
@@ -16354,8 +16538,12 @@
           <t>Hareskovgård</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
+      <c r="U88" t="n">
+        <v>55.759540142335</v>
+      </c>
+      <c r="V88" t="n">
+        <v>12.3880574948221</v>
+      </c>
       <c r="W88" t="n">
         <v>132</v>
       </c>
@@ -16443,8 +16631,12 @@
           <t>Hareskovgård</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
+      <c r="U89" t="n">
+        <v>55.759540142335</v>
+      </c>
+      <c r="V89" t="n">
+        <v>12.3880574948221</v>
+      </c>
       <c r="W89" t="n">
         <v>132</v>
       </c>
@@ -16532,8 +16724,12 @@
           <t>132 KV STATION DYREGÅRD</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
+      <c r="U90" t="n">
+        <v>55.7471878040055</v>
+      </c>
+      <c r="V90" t="n">
+        <v>12.3850960105833</v>
+      </c>
       <c r="W90" t="n">
         <v>132</v>
       </c>
@@ -16621,8 +16817,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
+      <c r="U91" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="V91" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="W91" t="n">
         <v>132</v>
       </c>
@@ -16710,8 +16910,12 @@
           <t>Glentegård</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
+      <c r="U92" t="n">
+        <v>55.7611873025953</v>
+      </c>
+      <c r="V92" t="n">
+        <v>12.5371757349425</v>
+      </c>
       <c r="W92" t="n">
         <v>132</v>
       </c>
@@ -16892,8 +17096,12 @@
           <t>132 KV SVANEMØLLE KBST</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
+      <c r="U94" t="n">
+        <v>55.7144797446461</v>
+      </c>
+      <c r="V94" t="n">
+        <v>12.5878763748329</v>
+      </c>
       <c r="W94" t="n">
         <v>132</v>
       </c>
@@ -17159,8 +17367,12 @@
           <t>400 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
+      <c r="U97" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="V97" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="W97" t="n">
         <v>400</v>
       </c>
@@ -17992,8 +18204,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
+      <c r="U106" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="V106" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="W106" t="n">
         <v>132</v>
       </c>
@@ -18356,8 +18572,12 @@
           <t>Ejbygård</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
+      <c r="U110" t="n">
+        <v>55.7020042516207</v>
+      </c>
+      <c r="V110" t="n">
+        <v>12.4051289650067</v>
+      </c>
       <c r="W110" t="n">
         <v>132</v>
       </c>
@@ -18699,8 +18919,12 @@
           <t>132 KV STATION DYREGÅRD</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>55.7471878040055</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>12.3850960105833</v>
+      </c>
       <c r="R114" t="n">
         <v>132</v>
       </c>
@@ -18712,8 +18936,12 @@
           <t>Ejbygård</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
+      <c r="U114" t="n">
+        <v>55.7020042516207</v>
+      </c>
+      <c r="V114" t="n">
+        <v>12.4051289650067</v>
+      </c>
       <c r="W114" t="n">
         <v>132</v>
       </c>
@@ -18784,8 +19012,12 @@
           <t>132 KV STATION DYREGÅRD</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>55.7471878040055</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>12.3850960105833</v>
+      </c>
       <c r="R115" t="n">
         <v>132</v>
       </c>
@@ -18797,8 +19029,12 @@
           <t>Hareskovgård</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
+      <c r="U115" t="n">
+        <v>55.759540142335</v>
+      </c>
+      <c r="V115" t="n">
+        <v>12.3880574948221</v>
+      </c>
       <c r="W115" t="n">
         <v>132</v>
       </c>
@@ -18869,8 +19105,12 @@
           <t>Ejbygård</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>55.7020042516207</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>12.4051289650067</v>
+      </c>
       <c r="R116" t="n">
         <v>132</v>
       </c>
@@ -18882,8 +19122,12 @@
           <t>Grønnegård</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
+      <c r="U116" t="n">
+        <v>55.7432900024616</v>
+      </c>
+      <c r="V116" t="n">
+        <v>12.4642636962795</v>
+      </c>
       <c r="W116" t="n">
         <v>132</v>
       </c>
@@ -18954,8 +19198,12 @@
           <t>Ejbygård</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
+      <c r="P117" t="n">
+        <v>55.7020042516207</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>12.4051289650067</v>
+      </c>
       <c r="R117" t="n">
         <v>132</v>
       </c>
@@ -18967,8 +19215,12 @@
           <t>Herstedgård</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
+      <c r="U117" t="n">
+        <v>55.6599589670042</v>
+      </c>
+      <c r="V117" t="n">
+        <v>12.3561289035921</v>
+      </c>
       <c r="W117" t="n">
         <v>132</v>
       </c>
@@ -19039,8 +19291,12 @@
           <t>Ejbygård</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>55.7020042516207</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>12.4051289650067</v>
+      </c>
       <c r="R118" t="n">
         <v>132</v>
       </c>
@@ -19593,8 +19849,12 @@
           <t>Flaskegård</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>55.5990778622218</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>12.2977578306887</v>
+      </c>
       <c r="R124" t="n">
         <v>132</v>
       </c>
@@ -19682,8 +19942,12 @@
           <t>Flaskegård</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>55.5990778622218</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>12.2977578306887</v>
+      </c>
       <c r="R125" t="n">
         <v>132</v>
       </c>
@@ -19771,8 +20035,12 @@
           <t>Flaskegård</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
+      <c r="P126" t="n">
+        <v>55.5990778622218</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>12.2977578306887</v>
+      </c>
       <c r="R126" t="n">
         <v>132</v>
       </c>
@@ -19860,8 +20128,12 @@
           <t>Flaskegård</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>55.5990778622218</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>12.2977578306887</v>
+      </c>
       <c r="R127" t="n">
         <v>132</v>
       </c>
@@ -19873,8 +20145,12 @@
           <t>Mosedegård</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
+      <c r="U127" t="n">
+        <v>55.5685451629065</v>
+      </c>
+      <c r="V127" t="n">
+        <v>12.2742303637046</v>
+      </c>
       <c r="W127" t="n">
         <v>132</v>
       </c>
@@ -19945,8 +20221,12 @@
           <t>Flaskegård</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
+      <c r="P128" t="n">
+        <v>55.5990778622218</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>12.2977578306887</v>
+      </c>
       <c r="R128" t="n">
         <v>132</v>
       </c>
@@ -19958,8 +20238,12 @@
           <t>Ostedgård</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
+      <c r="U128" t="n">
+        <v>55.6705744166352</v>
+      </c>
+      <c r="V128" t="n">
+        <v>11.9453047753712</v>
+      </c>
       <c r="W128" t="n">
         <v>132</v>
       </c>
@@ -20216,8 +20500,12 @@
           <t>Glentegård</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>55.7611873025953</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>12.5371757349425</v>
+      </c>
       <c r="R131" t="n">
         <v>132</v>
       </c>
@@ -20229,8 +20517,12 @@
           <t>132 KV SVANEMØLLE KBST</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
+      <c r="U131" t="n">
+        <v>55.7144797446461</v>
+      </c>
+      <c r="V131" t="n">
+        <v>12.5878763748329</v>
+      </c>
       <c r="W131" t="n">
         <v>132</v>
       </c>
@@ -20301,8 +20593,12 @@
           <t>Glentegård</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>55.7611873025953</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>12.5371757349425</v>
+      </c>
       <c r="R132" t="n">
         <v>132</v>
       </c>
@@ -20390,8 +20686,12 @@
           <t>Glentegård</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
+      <c r="P133" t="n">
+        <v>55.7611873025953</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>12.5371757349425</v>
+      </c>
       <c r="R133" t="n">
         <v>400</v>
       </c>
@@ -20403,8 +20703,12 @@
           <t>400 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
+      <c r="U133" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="V133" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="W133" t="n">
         <v>400</v>
       </c>
@@ -20585,8 +20889,12 @@
           <t>400 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
+      <c r="U135" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="V135" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="W135" t="n">
         <v>400</v>
       </c>
@@ -21025,8 +21333,12 @@
           <t>Hedegård</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>55.6530094301176</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>12.1048418993376</v>
+      </c>
       <c r="R140" t="n">
         <v>132</v>
       </c>
@@ -21114,8 +21426,12 @@
           <t>Hedegård</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
+      <c r="P141" t="n">
+        <v>55.6530094301176</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>12.1048418993376</v>
+      </c>
       <c r="R141" t="n">
         <v>132</v>
       </c>
@@ -21127,8 +21443,12 @@
           <t>KARA Novoren Roskilde</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
+      <c r="U141" t="n">
+        <v>55.6476215230415</v>
+      </c>
+      <c r="V141" t="n">
+        <v>12.1207776388374</v>
+      </c>
       <c r="W141" t="n">
         <v>132</v>
       </c>
@@ -21199,8 +21519,12 @@
           <t>Hedegård</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
+      <c r="P142" t="n">
+        <v>55.6530094301176</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>12.1048418993376</v>
+      </c>
       <c r="R142" t="n">
         <v>132</v>
       </c>
@@ -21474,8 +21798,12 @@
           <t>400 KV KOBLINGSSTATION HERSLEV</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
+      <c r="P145" t="n">
+        <v>55.5217287348645</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>11.3420209912948</v>
+      </c>
       <c r="R145" t="n">
         <v>400</v>
       </c>
@@ -21487,8 +21815,12 @@
           <t>400 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
+      <c r="U145" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="V145" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="W145" t="n">
         <v>400</v>
       </c>
@@ -21745,8 +22077,12 @@
           <t>Hareskovgård</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
+      <c r="P148" t="n">
+        <v>55.759540142335</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>12.3880574948221</v>
+      </c>
       <c r="R148" t="n">
         <v>132</v>
       </c>
@@ -21834,8 +22170,12 @@
           <t>Herstedgård</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>55.6599589670042</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>12.3561289035921</v>
+      </c>
       <c r="R149" t="n">
         <v>132</v>
       </c>
@@ -21848,10 +22188,10 @@
         </is>
       </c>
       <c r="U149" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
       <c r="V149" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="W149" t="n">
         <v>132</v>
@@ -21923,8 +22263,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
+      <c r="P150" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R150" t="n">
         <v>132</v>
       </c>
@@ -22012,8 +22356,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
+      <c r="P151" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R151" t="n">
         <v>132</v>
       </c>
@@ -22101,8 +22449,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
+      <c r="P152" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R152" t="n">
         <v>132</v>
       </c>
@@ -22190,8 +22542,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
+      <c r="P153" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R153" t="n">
         <v>132</v>
       </c>
@@ -22279,8 +22635,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
+      <c r="P154" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R154" t="n">
         <v>132</v>
       </c>
@@ -22293,10 +22653,10 @@
         </is>
       </c>
       <c r="U154" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
       <c r="V154" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="W154" t="n">
         <v>132</v>
@@ -22368,8 +22728,12 @@
           <t>132 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
+      <c r="P155" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R155" t="n">
         <v>132</v>
       </c>
@@ -22382,10 +22746,10 @@
         </is>
       </c>
       <c r="U155" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
       <c r="V155" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="W155" t="n">
         <v>132</v>
@@ -22457,8 +22821,12 @@
           <t>400 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
+      <c r="P156" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R156" t="n">
         <v>400</v>
       </c>
@@ -22546,8 +22914,12 @@
           <t>400 KV STATION HOVEGÅRD</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
+      <c r="P157" t="n">
+        <v>55.7893040846295</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>12.2272856189554</v>
+      </c>
       <c r="R157" t="n">
         <v>400</v>
       </c>
@@ -22653,10 +23025,10 @@
         </is>
       </c>
       <c r="U158" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
       <c r="V158" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="W158" t="n">
         <v>132</v>
@@ -23109,8 +23481,12 @@
           <t>Kirkeskovgård</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
+      <c r="U163" t="n">
+        <v>55.6248540827926</v>
+      </c>
+      <c r="V163" t="n">
+        <v>11.8863748101793</v>
+      </c>
       <c r="W163" t="n">
         <v>132</v>
       </c>
@@ -23744,8 +24120,12 @@
           <t>Mosedegård</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
+      <c r="U170" t="n">
+        <v>55.5685451629065</v>
+      </c>
+      <c r="V170" t="n">
+        <v>12.2742303637046</v>
+      </c>
       <c r="W170" t="n">
         <v>132</v>
       </c>
@@ -23816,8 +24196,12 @@
           <t>Kirkeskovgård</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
+      <c r="P171" t="n">
+        <v>55.6248540827926</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>11.8863748101793</v>
+      </c>
       <c r="R171" t="n">
         <v>132</v>
       </c>
@@ -23901,8 +24285,12 @@
           <t>Kirkeskovgård</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
+      <c r="P172" t="n">
+        <v>55.6248540827926</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>11.8863748101793</v>
+      </c>
       <c r="R172" t="n">
         <v>132</v>
       </c>
@@ -23986,8 +24374,12 @@
           <t>Kirkeskovgård</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
+      <c r="P173" t="n">
+        <v>55.6248540827926</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>11.8863748101793</v>
+      </c>
       <c r="R173" t="n">
         <v>132</v>
       </c>
@@ -24000,10 +24392,10 @@
         </is>
       </c>
       <c r="U173" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
       <c r="V173" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="W173" t="n">
         <v>132</v>
@@ -25001,8 +25393,12 @@
           <t>Novo Syd</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
+      <c r="P184" t="n">
+        <v>55.6873745837978</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>11.1176852759734</v>
+      </c>
       <c r="R184" t="n">
         <v>132</v>
       </c>
@@ -25281,8 +25677,12 @@
           <t>Ostedgård</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
+      <c r="U187" t="n">
+        <v>55.6705744166352</v>
+      </c>
+      <c r="V187" t="n">
+        <v>11.9453047753712</v>
+      </c>
       <c r="W187" t="n">
         <v>132</v>
       </c>
@@ -26733,10 +27133,10 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>55.629</v>
+        <v>55.6563742726452</v>
       </c>
       <c r="Q203" t="n">
-        <v>12.401</v>
+        <v>12.3419829488692</v>
       </c>
       <c r="R203" t="n">
         <v>132</v>
@@ -28286,8 +28686,12 @@
           <t>150 KV STATION ÅDALEN</t>
         </is>
       </c>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
+      <c r="P221" t="n">
+        <v>57.0217673874711</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>9.907020240291439</v>
+      </c>
       <c r="R221" t="n">
         <v>165</v>
       </c>
@@ -28375,8 +28779,12 @@
           <t>150 KV STATION ÅDALEN</t>
         </is>
       </c>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
+      <c r="P222" t="n">
+        <v>57.0217673874711</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>9.907020240291439</v>
+      </c>
       <c r="R222" t="n">
         <v>165</v>
       </c>
@@ -28388,8 +28796,12 @@
           <t>150 KV STATION HÅNDVÆRKERVEJ</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr"/>
-      <c r="V222" t="inlineStr"/>
+      <c r="U222" t="n">
+        <v>57.0463253989495</v>
+      </c>
+      <c r="V222" t="n">
+        <v>9.91458276509298</v>
+      </c>
       <c r="W222" t="n">
         <v>165</v>
       </c>
@@ -28460,8 +28872,12 @@
           <t>150 KV STATION ÅDALEN</t>
         </is>
       </c>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
+      <c r="P223" t="n">
+        <v>57.0217673874711</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>9.907020240291439</v>
+      </c>
       <c r="R223" t="n">
         <v>165</v>
       </c>
@@ -33664,8 +34080,12 @@
           <t>150 KV STATION RYTTERGÅRD</t>
         </is>
       </c>
-      <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="inlineStr"/>
+      <c r="P279" t="n">
+        <v>55.5984310487063</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>9.73224881349171</v>
+      </c>
       <c r="R279" t="n">
         <v>165</v>
       </c>
@@ -33753,8 +34173,12 @@
           <t>150 KV STATION HASLE</t>
         </is>
       </c>
-      <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="inlineStr"/>
+      <c r="P280" t="n">
+        <v>56.1904355183995</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>10.16805</v>
+      </c>
       <c r="R280" t="n">
         <v>165</v>
       </c>
@@ -33838,8 +34262,12 @@
           <t>150 KV STATION HASLE</t>
         </is>
       </c>
-      <c r="P281" t="inlineStr"/>
-      <c r="Q281" t="inlineStr"/>
+      <c r="P281" t="n">
+        <v>56.1904355183995</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>10.16805</v>
+      </c>
       <c r="R281" t="n">
         <v>165</v>
       </c>
@@ -33851,8 +34279,12 @@
           <t>150 KV STATION MOLLERUP</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr"/>
-      <c r="V281" t="inlineStr"/>
+      <c r="U281" t="n">
+        <v>56.225273912857</v>
+      </c>
+      <c r="V281" t="n">
+        <v>10.2190107413707</v>
+      </c>
       <c r="W281" t="n">
         <v>165</v>
       </c>
@@ -33923,8 +34355,12 @@
           <t>150 KV STATION HASLE</t>
         </is>
       </c>
-      <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="inlineStr"/>
+      <c r="P282" t="n">
+        <v>56.1904355183995</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>10.16805</v>
+      </c>
       <c r="R282" t="n">
         <v>165</v>
       </c>
@@ -33936,8 +34372,12 @@
           <t>150 KV STATION HØSKOV</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr"/>
-      <c r="V282" t="inlineStr"/>
+      <c r="U282" t="n">
+        <v>56.1493883098031</v>
+      </c>
+      <c r="V282" t="n">
+        <v>10.1426557207713</v>
+      </c>
       <c r="W282" t="n">
         <v>165</v>
       </c>
@@ -34380,8 +34820,12 @@
           <t>150 KV STATION HORNBÆK</t>
         </is>
       </c>
-      <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="inlineStr"/>
+      <c r="P287" t="n">
+        <v>56.482077640062</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>9.95490572883609</v>
+      </c>
       <c r="R287" t="n">
         <v>165</v>
       </c>
@@ -34469,8 +34913,12 @@
           <t>150 KV STATION HORNBÆK</t>
         </is>
       </c>
-      <c r="P288" t="inlineStr"/>
-      <c r="Q288" t="inlineStr"/>
+      <c r="P288" t="n">
+        <v>56.482077640062</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>9.95490572883609</v>
+      </c>
       <c r="R288" t="n">
         <v>165</v>
       </c>
@@ -34651,8 +35099,12 @@
           <t>150 KV STATION HØSKOV</t>
         </is>
       </c>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
+      <c r="P290" t="n">
+        <v>56.1493883098031</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>10.1426557207713</v>
+      </c>
       <c r="R290" t="n">
         <v>165</v>
       </c>
@@ -35036,8 +35488,12 @@
           <t>150 KV STATION SKANSEN</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr"/>
-      <c r="V294" t="inlineStr"/>
+      <c r="U294" t="n">
+        <v>57.0715877870094</v>
+      </c>
+      <c r="V294" t="n">
+        <v>9.931709330517711</v>
+      </c>
       <c r="W294" t="n">
         <v>165</v>
       </c>
@@ -35108,8 +35564,12 @@
           <t>150 KV STATION HÅNDVÆRKERVEJ</t>
         </is>
       </c>
-      <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="inlineStr"/>
+      <c r="P295" t="n">
+        <v>57.0463253989495</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>9.91458276509298</v>
+      </c>
       <c r="R295" t="n">
         <v>165</v>
       </c>
@@ -37535,8 +37995,12 @@
           <t>150 KV STATION RYTTERGÅRD</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr"/>
-      <c r="V321" t="inlineStr"/>
+      <c r="U321" t="n">
+        <v>55.5984310487063</v>
+      </c>
+      <c r="V321" t="n">
+        <v>9.73224881349171</v>
+      </c>
       <c r="W321" t="n">
         <v>165</v>
       </c>
@@ -38157,8 +38621,12 @@
           <t>Lemkær</t>
         </is>
       </c>
-      <c r="P328" t="inlineStr"/>
-      <c r="Q328" t="inlineStr"/>
+      <c r="P328" t="n">
+        <v>56.1093866151184</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>8.353226184389969</v>
+      </c>
       <c r="R328" t="n">
         <v>165</v>
       </c>
@@ -38242,8 +38710,12 @@
           <t>Lemkær</t>
         </is>
       </c>
-      <c r="P329" t="inlineStr"/>
-      <c r="Q329" t="inlineStr"/>
+      <c r="P329" t="n">
+        <v>56.1093866151184</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>8.353226184389969</v>
+      </c>
       <c r="R329" t="n">
         <v>165</v>
       </c>
@@ -38699,8 +39171,12 @@
           <t>150 KV STATION MESBALLE</t>
         </is>
       </c>
-      <c r="P334" t="inlineStr"/>
-      <c r="Q334" t="inlineStr"/>
+      <c r="P334" t="n">
+        <v>56.435023192998</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>10.4987386757303</v>
+      </c>
       <c r="R334" t="n">
         <v>165</v>
       </c>
@@ -38788,8 +39264,12 @@
           <t>150 KV STATION MESBALLE</t>
         </is>
       </c>
-      <c r="P335" t="inlineStr"/>
-      <c r="Q335" t="inlineStr"/>
+      <c r="P335" t="n">
+        <v>56.435023192998</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>10.4987386757303</v>
+      </c>
       <c r="R335" t="n">
         <v>165</v>
       </c>
@@ -39245,8 +39725,12 @@
           <t>150 KV STATION MOLLERUP</t>
         </is>
       </c>
-      <c r="P340" t="inlineStr"/>
-      <c r="Q340" t="inlineStr"/>
+      <c r="P340" t="n">
+        <v>56.225273912857</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>10.2190107413707</v>
+      </c>
       <c r="R340" t="n">
         <v>165</v>
       </c>
@@ -39334,8 +39818,12 @@
           <t>150 KV STATION MOSELUND</t>
         </is>
       </c>
-      <c r="P341" t="inlineStr"/>
-      <c r="Q341" t="inlineStr"/>
+      <c r="P341" t="n">
+        <v>56.4297672454752</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>10.0985712474414</v>
+      </c>
       <c r="R341" t="n">
         <v>165</v>
       </c>
@@ -40260,8 +40748,12 @@
           <t>150 KV STATION RYTTERGÅRD</t>
         </is>
       </c>
-      <c r="P351" t="inlineStr"/>
-      <c r="Q351" t="inlineStr"/>
+      <c r="P351" t="n">
+        <v>55.5984310487063</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>9.73224881349171</v>
+      </c>
       <c r="R351" t="n">
         <v>165</v>
       </c>
